--- a/stick-world/config/excel/建筑数据.xlsx
+++ b/stick-world/config/excel/建筑数据.xlsx
@@ -7,7 +7,7 @@
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="buildings" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="建筑" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>

--- a/stick-world/config/excel/建筑数据.xlsx
+++ b/stick-world/config/excel/建筑数据.xlsx
@@ -440,7 +440,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M8"/>
+  <dimension ref="A1:J8"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -459,440 +459,344 @@
   </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" s="1" t="inlineStr">
+      <c r="A1" t="inlineStr">
         <is>
           <t>id</t>
         </is>
       </c>
-      <c r="B1" s="1" t="inlineStr">
+      <c r="B1" t="inlineStr">
         <is>
           <t>name_zh</t>
         </is>
       </c>
-      <c r="C1" s="1" t="inlineStr">
+      <c r="C1" t="inlineStr">
         <is>
           <t>type</t>
         </is>
       </c>
-      <c r="D1" s="1" t="inlineStr">
+      <c r="D1" t="inlineStr">
         <is>
           <t>tier</t>
         </is>
       </c>
-      <c r="E1" s="1" t="inlineStr">
-        <is>
-          <t>build_time</t>
-        </is>
-      </c>
-      <c r="F1" s="1" t="inlineStr">
-        <is>
-          <t>build_cost_food</t>
-        </is>
-      </c>
-      <c r="G1" s="1" t="inlineStr">
+      <c r="E1" t="inlineStr">
+        <is>
+          <t>build_workload</t>
+        </is>
+      </c>
+      <c r="F1" t="inlineStr">
         <is>
           <t>build_cost_wood</t>
         </is>
       </c>
-      <c r="H1" s="1" t="inlineStr">
+      <c r="G1" t="inlineStr">
         <is>
           <t>build_cost_stone</t>
         </is>
       </c>
-      <c r="I1" s="1" t="inlineStr">
+      <c r="H1" t="inlineStr">
         <is>
           <t>build_cost_metal</t>
         </is>
       </c>
-      <c r="J1" s="1" t="inlineStr">
+      <c r="I1" t="inlineStr">
         <is>
           <t>max_hp</t>
         </is>
       </c>
-      <c r="K1" s="1" t="inlineStr">
-        <is>
-          <t>workers_required</t>
-        </is>
-      </c>
-      <c r="L1" s="1" t="inlineStr">
-        <is>
-          <t>unlocked_by_tech</t>
-        </is>
-      </c>
-      <c r="M1" s="1" t="inlineStr">
+      <c r="J1" t="inlineStr">
         <is>
           <t>description</t>
         </is>
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="1" t="inlineStr">
+      <c r="A2" t="inlineStr">
         <is>
           <t>ID</t>
         </is>
       </c>
-      <c r="B2" s="1" t="inlineStr">
+      <c r="B2" t="inlineStr">
         <is>
           <t>名称</t>
         </is>
       </c>
-      <c r="C2" s="1" t="inlineStr">
+      <c r="C2" t="inlineStr">
         <is>
           <t>类型</t>
         </is>
       </c>
-      <c r="D2" s="1" t="inlineStr">
+      <c r="D2" t="inlineStr">
         <is>
           <t>等级</t>
         </is>
       </c>
-      <c r="E2" s="1" t="inlineStr">
-        <is>
-          <t>建造时间</t>
-        </is>
-      </c>
-      <c r="F2" s="1" t="inlineStr">
-        <is>
-          <t>食物消耗</t>
-        </is>
-      </c>
-      <c r="G2" s="1" t="inlineStr">
+      <c r="E2" t="inlineStr">
+        <is>
+          <t>工程量(单位待定)</t>
+        </is>
+      </c>
+      <c r="F2" t="inlineStr">
         <is>
           <t>木材消耗</t>
         </is>
       </c>
-      <c r="H2" s="1" t="inlineStr">
+      <c r="G2" t="inlineStr">
         <is>
           <t>石料消耗</t>
         </is>
       </c>
-      <c r="I2" s="1" t="inlineStr">
+      <c r="H2" t="inlineStr">
         <is>
           <t>金属消耗</t>
         </is>
       </c>
-      <c r="J2" s="1" t="inlineStr">
+      <c r="I2" t="inlineStr">
         <is>
           <t>最大生命值</t>
         </is>
       </c>
-      <c r="K2" s="1" t="inlineStr">
-        <is>
-          <t>所需工人</t>
-        </is>
-      </c>
-      <c r="L2" s="1" t="inlineStr">
-        <is>
-          <t>解锁科技</t>
-        </is>
-      </c>
-      <c r="M2" s="1" t="inlineStr">
+      <c r="J2" t="inlineStr">
         <is>
           <t>描述</t>
         </is>
       </c>
     </row>
     <row r="3">
-      <c r="A3" s="2" t="inlineStr">
+      <c r="A3" t="inlineStr">
         <is>
           <t>bld_house</t>
         </is>
       </c>
-      <c r="B3" s="2" t="inlineStr">
+      <c r="B3" t="inlineStr">
         <is>
           <t>民居</t>
         </is>
       </c>
-      <c r="C3" s="2" t="inlineStr">
+      <c r="C3" t="inlineStr">
         <is>
           <t>house</t>
         </is>
       </c>
-      <c r="D3" s="2" t="n">
+      <c r="D3" t="n">
         <v>1</v>
       </c>
-      <c r="E3" s="2" t="n">
+      <c r="E3" t="n">
         <v>30</v>
       </c>
-      <c r="F3" s="2" t="n">
+      <c r="F3" t="n">
+        <v>100</v>
+      </c>
+      <c r="G3" t="n">
         <v>50</v>
       </c>
-      <c r="G3" s="2" t="n">
-        <v>100</v>
-      </c>
-      <c r="H3" s="2" t="n">
-        <v>50</v>
-      </c>
-      <c r="I3" s="2" t="n">
+      <c r="H3" t="n">
         <v>0</v>
       </c>
-      <c r="J3" s="2" t="n">
+      <c r="I3" t="n">
         <v>200</v>
       </c>
-      <c r="K3" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="L3" s="2" t="inlineStr">
-        <is>
-          <t>none</t>
-        </is>
-      </c>
-      <c r="M3" s="2" t="inlineStr">
+      <c r="J3" t="inlineStr">
         <is>
           <t>提供人口居住空间</t>
         </is>
       </c>
     </row>
     <row r="4">
-      <c r="A4" s="2" t="inlineStr">
+      <c r="A4" t="inlineStr">
         <is>
           <t>bld_farm</t>
         </is>
       </c>
-      <c r="B4" s="2" t="inlineStr">
+      <c r="B4" t="inlineStr">
         <is>
           <t>农场</t>
         </is>
       </c>
-      <c r="C4" s="2" t="inlineStr">
+      <c r="C4" t="inlineStr">
         <is>
           <t>farm</t>
         </is>
       </c>
-      <c r="D4" s="2" t="n">
+      <c r="D4" t="n">
         <v>1</v>
       </c>
-      <c r="E4" s="2" t="n">
+      <c r="E4" t="n">
         <v>45</v>
       </c>
-      <c r="F4" s="2" t="n">
-        <v>20</v>
-      </c>
-      <c r="G4" s="2" t="n">
+      <c r="F4" t="n">
         <v>80</v>
       </c>
-      <c r="H4" s="2" t="n">
+      <c r="G4" t="n">
         <v>30</v>
       </c>
-      <c r="I4" s="2" t="n">
+      <c r="H4" t="n">
         <v>0</v>
       </c>
-      <c r="J4" s="2" t="n">
+      <c r="I4" t="n">
         <v>150</v>
       </c>
-      <c r="K4" s="2" t="n">
-        <v>2</v>
-      </c>
-      <c r="L4" s="2" t="inlineStr">
-        <is>
-          <t>tech_agriculture</t>
-        </is>
-      </c>
-      <c r="M4" s="2" t="inlineStr">
+      <c r="J4" t="inlineStr">
         <is>
           <t>生产食物资源</t>
         </is>
       </c>
     </row>
     <row r="5">
-      <c r="A5" s="2" t="inlineStr">
+      <c r="A5" t="inlineStr">
         <is>
           <t>bld_workshop</t>
         </is>
       </c>
-      <c r="B5" s="2" t="inlineStr">
+      <c r="B5" t="inlineStr">
         <is>
           <t>工坊</t>
         </is>
       </c>
-      <c r="C5" s="2" t="inlineStr">
+      <c r="C5" t="inlineStr">
         <is>
           <t>workshop</t>
         </is>
       </c>
-      <c r="D5" s="2" t="n">
+      <c r="D5" t="n">
         <v>2</v>
       </c>
-      <c r="E5" s="2" t="n">
+      <c r="E5" t="n">
         <v>60</v>
       </c>
-      <c r="F5" s="2" t="n">
-        <v>30</v>
-      </c>
-      <c r="G5" s="2" t="n">
+      <c r="F5" t="n">
         <v>120</v>
       </c>
-      <c r="H5" s="2" t="n">
+      <c r="G5" t="n">
         <v>60</v>
       </c>
-      <c r="I5" s="2" t="n">
+      <c r="H5" t="n">
         <v>20</v>
       </c>
-      <c r="J5" s="2" t="n">
+      <c r="I5" t="n">
         <v>300</v>
       </c>
-      <c r="K5" s="2" t="n">
-        <v>3</v>
-      </c>
-      <c r="L5" s="2" t="inlineStr">
-        <is>
-          <t>tech_crafting</t>
-        </is>
-      </c>
-      <c r="M5" s="2" t="inlineStr">
+      <c r="J5" t="inlineStr">
         <is>
           <t>加工基础资源为高级资源</t>
         </is>
       </c>
     </row>
     <row r="6">
-      <c r="A6" s="2" t="inlineStr">
+      <c r="A6" t="inlineStr">
         <is>
           <t>bld_barracks</t>
         </is>
       </c>
-      <c r="B6" s="2" t="inlineStr">
+      <c r="B6" t="inlineStr">
         <is>
           <t>兵营</t>
         </is>
       </c>
-      <c r="C6" s="2" t="inlineStr">
+      <c r="C6" t="inlineStr">
         <is>
           <t>barracks</t>
         </is>
       </c>
-      <c r="D6" s="2" t="n">
+      <c r="D6" t="n">
         <v>2</v>
       </c>
-      <c r="E6" s="2" t="n">
+      <c r="E6" t="n">
         <v>90</v>
       </c>
-      <c r="F6" s="2" t="n">
-        <v>80</v>
-      </c>
-      <c r="G6" s="2" t="n">
+      <c r="F6" t="n">
         <v>150</v>
       </c>
-      <c r="H6" s="2" t="n">
+      <c r="G6" t="n">
         <v>100</v>
       </c>
-      <c r="I6" s="2" t="n">
+      <c r="H6" t="n">
         <v>50</v>
       </c>
-      <c r="J6" s="2" t="n">
+      <c r="I6" t="n">
         <v>500</v>
       </c>
-      <c r="K6" s="2" t="n">
-        <v>5</v>
-      </c>
-      <c r="L6" s="2" t="inlineStr">
-        <is>
-          <t>tech_military_1</t>
-        </is>
-      </c>
-      <c r="M6" s="2" t="inlineStr">
+      <c r="J6" t="inlineStr">
         <is>
           <t>训练战斗单位</t>
         </is>
       </c>
     </row>
     <row r="7">
-      <c r="A7" s="2" t="inlineStr">
+      <c r="A7" t="inlineStr">
         <is>
           <t>bld_market</t>
         </is>
       </c>
-      <c r="B7" s="2" t="inlineStr">
+      <c r="B7" t="inlineStr">
         <is>
           <t>集市</t>
         </is>
       </c>
-      <c r="C7" s="2" t="inlineStr">
+      <c r="C7" t="inlineStr">
         <is>
           <t>market</t>
         </is>
       </c>
-      <c r="D7" s="2" t="n">
+      <c r="D7" t="n">
         <v>2</v>
       </c>
-      <c r="E7" s="2" t="n">
+      <c r="E7" t="n">
         <v>50</v>
       </c>
-      <c r="F7" s="2" t="n">
-        <v>100</v>
-      </c>
-      <c r="G7" s="2" t="n">
+      <c r="F7" t="n">
         <v>80</v>
       </c>
-      <c r="H7" s="2" t="n">
+      <c r="G7" t="n">
         <v>40</v>
       </c>
-      <c r="I7" s="2" t="n">
+      <c r="H7" t="n">
         <v>10</v>
       </c>
-      <c r="J7" s="2" t="n">
+      <c r="I7" t="n">
         <v>250</v>
       </c>
-      <c r="K7" s="2" t="n">
-        <v>2</v>
-      </c>
-      <c r="L7" s="2" t="inlineStr">
-        <is>
-          <t>tech_trade</t>
-        </is>
-      </c>
-      <c r="M7" s="2" t="inlineStr">
+      <c r="J7" t="inlineStr">
         <is>
           <t>进行资源交易</t>
         </is>
       </c>
     </row>
     <row r="8">
-      <c r="A8" s="2" t="inlineStr">
+      <c r="A8" t="inlineStr">
         <is>
           <t>bld_academy</t>
         </is>
       </c>
-      <c r="B8" s="2" t="inlineStr">
+      <c r="B8" t="inlineStr">
         <is>
           <t>学院</t>
         </is>
       </c>
-      <c r="C8" s="2" t="inlineStr">
+      <c r="C8" t="inlineStr">
         <is>
           <t>academy</t>
         </is>
       </c>
-      <c r="D8" s="2" t="n">
+      <c r="D8" t="n">
         <v>3</v>
       </c>
-      <c r="E8" s="2" t="n">
+      <c r="E8" t="n">
         <v>120</v>
       </c>
-      <c r="F8" s="2" t="n">
+      <c r="F8" t="n">
+        <v>200</v>
+      </c>
+      <c r="G8" t="n">
         <v>150</v>
       </c>
-      <c r="G8" s="2" t="n">
-        <v>200</v>
-      </c>
-      <c r="H8" s="2" t="n">
-        <v>150</v>
-      </c>
-      <c r="I8" s="2" t="n">
+      <c r="H8" t="n">
         <v>80</v>
       </c>
-      <c r="J8" s="2" t="n">
+      <c r="I8" t="n">
         <v>600</v>
       </c>
-      <c r="K8" s="2" t="n">
-        <v>4</v>
-      </c>
-      <c r="L8" s="2" t="inlineStr">
-        <is>
-          <t>tech_education</t>
-        </is>
-      </c>
-      <c r="M8" s="2" t="inlineStr">
+      <c r="J8" t="inlineStr">
         <is>
           <t>研究科技</t>
         </is>

--- a/stick-world/config/excel/建筑数据.xlsx
+++ b/stick-world/config/excel/建筑数据.xlsx
@@ -412,7 +412,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J10"/>
+  <dimension ref="A1:R19"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15" outlineLevelRow="0"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -455,32 +455,72 @@
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>build_workload</t>
+          <t>width</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
+          <t>build_time</t>
+        </is>
+      </c>
+      <c r="G2" t="inlineStr">
+        <is>
           <t>build_cost_wood</t>
         </is>
       </c>
-      <c r="G2" t="inlineStr">
+      <c r="H2" t="inlineStr">
         <is>
           <t>build_cost_stone</t>
         </is>
       </c>
-      <c r="H2" t="inlineStr">
+      <c r="I2" t="inlineStr">
         <is>
           <t>build_cost_metal</t>
         </is>
       </c>
-      <c r="I2" t="inlineStr">
+      <c r="J2" t="inlineStr">
         <is>
           <t>max_hp</t>
         </is>
       </c>
-      <c r="J2" t="inlineStr">
+      <c r="K2" t="inlineStr">
+        <is>
+          <t>workers_required</t>
+        </is>
+      </c>
+      <c r="L2" t="inlineStr">
+        <is>
+          <t>interior_mode</t>
+        </is>
+      </c>
+      <c r="M2" t="inlineStr">
+        <is>
+          <t>mega_interior_map_id</t>
+        </is>
+      </c>
+      <c r="N2" t="inlineStr">
         <is>
           <t>description</t>
+        </is>
+      </c>
+      <c r="O2" t="inlineStr">
+        <is>
+          <t>unlocked_by_tech</t>
+        </is>
+      </c>
+      <c r="P2" t="inlineStr">
+        <is>
+          <t>wall_tier</t>
+        </is>
+      </c>
+      <c r="Q2" t="inlineStr">
+        <is>
+          <t>can_stand_on</t>
+        </is>
+      </c>
+      <c r="R2" t="inlineStr">
+        <is>
+          <t>is_gate</t>
         </is>
       </c>
     </row>
@@ -507,44 +547,84 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>工程量(单位待定)</t>
+          <t>width</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
+          <t>build_time</t>
+        </is>
+      </c>
+      <c r="G3" t="inlineStr">
+        <is>
           <t>木材消耗</t>
         </is>
       </c>
-      <c r="G3" t="inlineStr">
+      <c r="H3" t="inlineStr">
         <is>
           <t>石料消耗</t>
         </is>
       </c>
-      <c r="H3" t="inlineStr">
+      <c r="I3" t="inlineStr">
         <is>
           <t>金属消耗</t>
         </is>
       </c>
-      <c r="I3" t="inlineStr">
+      <c r="J3" t="inlineStr">
         <is>
           <t>最大生命值</t>
         </is>
       </c>
-      <c r="J3" t="inlineStr">
+      <c r="K3" t="inlineStr">
+        <is>
+          <t>workers_required</t>
+        </is>
+      </c>
+      <c r="L3" t="inlineStr">
+        <is>
+          <t>interior_mode</t>
+        </is>
+      </c>
+      <c r="M3" t="inlineStr">
+        <is>
+          <t>mega_interior_map_id</t>
+        </is>
+      </c>
+      <c r="N3" t="inlineStr">
         <is>
           <t>描述</t>
+        </is>
+      </c>
+      <c r="O3" t="inlineStr">
+        <is>
+          <t>unlocked_by_tech</t>
+        </is>
+      </c>
+      <c r="P3" t="inlineStr">
+        <is>
+          <t>wall_tier</t>
+        </is>
+      </c>
+      <c r="Q3" t="inlineStr">
+        <is>
+          <t>can_stand_on</t>
+        </is>
+      </c>
+      <c r="R3" t="inlineStr">
+        <is>
+          <t>is_gate</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>bld_house</t>
+          <t>house</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>住房</t>
+          <t>民居</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
@@ -556,21 +636,31 @@
         <v>1</v>
       </c>
       <c r="E4" t="n">
+        <v>2</v>
+      </c>
+      <c r="F4" t="n">
         <v>30</v>
       </c>
-      <c r="F4" t="n">
+      <c r="G4" t="n">
         <v>100</v>
       </c>
-      <c r="G4" t="n">
+      <c r="H4" t="n">
         <v>50</v>
       </c>
-      <c r="H4" t="n">
-        <v>0</v>
-      </c>
       <c r="I4" t="n">
+        <v>0</v>
+      </c>
+      <c r="J4" t="n">
         <v>200</v>
       </c>
-      <c r="J4" t="inlineStr">
+      <c r="K4" t="n">
+        <v>0</v>
+      </c>
+      <c r="L4" t="n">
+        <v>0</v>
+      </c>
+      <c r="M4" t="inlineStr"/>
+      <c r="N4" t="inlineStr">
         <is>
           <t>提供人口居住空间</t>
         </is>
@@ -579,12 +669,12 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>bld_farm</t>
+          <t>farm</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>铁匠铺</t>
+          <t>农场</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -596,75 +686,100 @@
         <v>1</v>
       </c>
       <c r="E5" t="n">
+        <v>3</v>
+      </c>
+      <c r="F5" t="n">
         <v>45</v>
       </c>
-      <c r="F5" t="n">
+      <c r="G5" t="n">
         <v>80</v>
       </c>
-      <c r="G5" t="n">
+      <c r="H5" t="n">
         <v>30</v>
       </c>
-      <c r="H5" t="n">
-        <v>0</v>
-      </c>
       <c r="I5" t="n">
+        <v>0</v>
+      </c>
+      <c r="J5" t="n">
         <v>150</v>
       </c>
-      <c r="J5" t="inlineStr">
+      <c r="K5" t="n">
+        <v>2</v>
+      </c>
+      <c r="L5" t="n">
+        <v>0</v>
+      </c>
+      <c r="M5" t="inlineStr"/>
+      <c r="N5" t="inlineStr">
         <is>
           <t>生产食物资源</t>
+        </is>
+      </c>
+      <c r="O5" t="inlineStr">
+        <is>
+          <t>tech_agriculture</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>bld_workshop</t>
+          <t>placeholder</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>行政中心</t>
+          <t>草棚</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>workshop</t>
+          <t>house</t>
         </is>
       </c>
       <c r="D6" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E6" t="n">
-        <v>60</v>
+        <v>16</v>
       </c>
       <c r="F6" t="n">
-        <v>120</v>
+        <v>30</v>
       </c>
       <c r="G6" t="n">
-        <v>60</v>
+        <v>20</v>
       </c>
       <c r="H6" t="n">
-        <v>20</v>
+        <v>0</v>
       </c>
       <c r="I6" t="n">
-        <v>300</v>
-      </c>
-      <c r="J6" t="inlineStr">
-        <is>
-          <t>加工基础资源为高级资源</t>
+        <v>0</v>
+      </c>
+      <c r="J6" t="n">
+        <v>100</v>
+      </c>
+      <c r="K6" t="n">
+        <v>0</v>
+      </c>
+      <c r="L6" t="n">
+        <v>0</v>
+      </c>
+      <c r="M6" t="inlineStr"/>
+      <c r="N6" t="inlineStr">
+        <is>
+          <t>标准的茅草屋外壳，可自由调节宽度</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>bld_barracks</t>
+          <t>barracks</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>武器库</t>
+          <t>兵营</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
@@ -676,30 +791,45 @@
         <v>2</v>
       </c>
       <c r="E7" t="n">
+        <v>16</v>
+      </c>
+      <c r="F7" t="n">
         <v>90</v>
       </c>
-      <c r="F7" t="n">
+      <c r="G7" t="n">
         <v>150</v>
       </c>
-      <c r="G7" t="n">
+      <c r="H7" t="n">
         <v>100</v>
       </c>
-      <c r="H7" t="n">
+      <c r="I7" t="n">
         <v>50</v>
       </c>
-      <c r="I7" t="n">
+      <c r="J7" t="n">
         <v>500</v>
       </c>
-      <c r="J7" t="inlineStr">
+      <c r="K7" t="n">
+        <v>5</v>
+      </c>
+      <c r="L7" t="n">
+        <v>0</v>
+      </c>
+      <c r="M7" t="inlineStr"/>
+      <c r="N7" t="inlineStr">
         <is>
           <t>训练战斗单位</t>
+        </is>
+      </c>
+      <c r="O7" t="inlineStr">
+        <is>
+          <t>tech_military_1</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>bld_market</t>
+          <t>market</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -716,30 +846,45 @@
         <v>2</v>
       </c>
       <c r="E8" t="n">
+        <v>2</v>
+      </c>
+      <c r="F8" t="n">
         <v>50</v>
       </c>
-      <c r="F8" t="n">
+      <c r="G8" t="n">
         <v>80</v>
       </c>
-      <c r="G8" t="n">
+      <c r="H8" t="n">
         <v>40</v>
       </c>
-      <c r="H8" t="n">
+      <c r="I8" t="n">
         <v>10</v>
       </c>
-      <c r="I8" t="n">
+      <c r="J8" t="n">
         <v>250</v>
       </c>
-      <c r="J8" t="inlineStr">
+      <c r="K8" t="n">
+        <v>2</v>
+      </c>
+      <c r="L8" t="n">
+        <v>0</v>
+      </c>
+      <c r="M8" t="inlineStr"/>
+      <c r="N8" t="inlineStr">
         <is>
           <t>进行资源交易</t>
+        </is>
+      </c>
+      <c r="O8" t="inlineStr">
+        <is>
+          <t>tech_trade</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>bld_academy</t>
+          <t>academy</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -756,30 +901,598 @@
         <v>3</v>
       </c>
       <c r="E9" t="n">
+        <v>3</v>
+      </c>
+      <c r="F9" t="n">
         <v>120</v>
       </c>
-      <c r="F9" t="n">
+      <c r="G9" t="n">
         <v>200</v>
       </c>
-      <c r="G9" t="n">
+      <c r="H9" t="n">
         <v>150</v>
       </c>
-      <c r="H9" t="n">
+      <c r="I9" t="n">
         <v>80</v>
       </c>
-      <c r="I9" t="n">
+      <c r="J9" t="n">
         <v>600</v>
       </c>
-      <c r="J9" t="inlineStr">
+      <c r="K9" t="n">
+        <v>4</v>
+      </c>
+      <c r="L9" t="n">
+        <v>0</v>
+      </c>
+      <c r="M9" t="inlineStr"/>
+      <c r="N9" t="inlineStr">
         <is>
           <t>研究科技</t>
         </is>
       </c>
+      <c r="O9" t="inlineStr">
+        <is>
+          <t>tech_education</t>
+        </is>
+      </c>
     </row>
     <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>smithy_lv1</t>
+        </is>
+      </c>
       <c r="B10" t="inlineStr">
         <is>
+          <t>铁匠铺 Lv1</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>smithy</t>
+        </is>
+      </c>
+      <c r="D10" t="n">
+        <v>1</v>
+      </c>
+      <c r="E10" t="n">
+        <v>2</v>
+      </c>
+      <c r="F10" t="n">
+        <v>60</v>
+      </c>
+      <c r="G10" t="n">
+        <v>100</v>
+      </c>
+      <c r="H10" t="n">
+        <v>80</v>
+      </c>
+      <c r="I10" t="n">
+        <v>40</v>
+      </c>
+      <c r="J10" t="n">
+        <v>350</v>
+      </c>
+      <c r="K10" t="n">
+        <v>2</v>
+      </c>
+      <c r="L10" t="n">
+        <v>0</v>
+      </c>
+      <c r="M10" t="inlineStr"/>
+      <c r="N10" t="inlineStr">
+        <is>
+          <t>锻造基础金属工具与武器</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>smithy_lv2</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>铁匠铺 Lv2</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>smithy</t>
+        </is>
+      </c>
+      <c r="D11" t="n">
+        <v>2</v>
+      </c>
+      <c r="E11" t="n">
+        <v>2</v>
+      </c>
+      <c r="F11" t="n">
+        <v>90</v>
+      </c>
+      <c r="G11" t="n">
+        <v>150</v>
+      </c>
+      <c r="H11" t="n">
+        <v>120</v>
+      </c>
+      <c r="I11" t="n">
+        <v>80</v>
+      </c>
+      <c r="J11" t="n">
+        <v>500</v>
+      </c>
+      <c r="K11" t="n">
+        <v>3</v>
+      </c>
+      <c r="L11" t="n">
+        <v>0</v>
+      </c>
+      <c r="M11" t="inlineStr"/>
+      <c r="N11" t="inlineStr">
+        <is>
+          <t>可锻造精良品质装备</t>
+        </is>
+      </c>
+      <c r="O11" t="inlineStr">
+        <is>
+          <t>tech_crafting</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>smithy_lv3</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>铁匠铺 Lv3</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>smithy</t>
+        </is>
+      </c>
+      <c r="D12" t="n">
+        <v>3</v>
+      </c>
+      <c r="E12" t="n">
+        <v>2</v>
+      </c>
+      <c r="F12" t="n">
+        <v>120</v>
+      </c>
+      <c r="G12" t="n">
+        <v>200</v>
+      </c>
+      <c r="H12" t="n">
+        <v>160</v>
+      </c>
+      <c r="I12" t="n">
+        <v>120</v>
+      </c>
+      <c r="J12" t="n">
+        <v>700</v>
+      </c>
+      <c r="K12" t="n">
+        <v>4</v>
+      </c>
+      <c r="L12" t="n">
+        <v>0</v>
+      </c>
+      <c r="M12" t="inlineStr"/>
+      <c r="N12" t="inlineStr">
+        <is>
+          <t>可锻造稀有品质装备</t>
+        </is>
+      </c>
+      <c r="O12" t="inlineStr">
+        <is>
+          <t>tech_metallurgy</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>smithy_lv4</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>铁匠铺 Lv4</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>smithy</t>
+        </is>
+      </c>
+      <c r="D13" t="n">
+        <v>4</v>
+      </c>
+      <c r="E13" t="n">
+        <v>2</v>
+      </c>
+      <c r="F13" t="n">
+        <v>180</v>
+      </c>
+      <c r="G13" t="n">
+        <v>300</v>
+      </c>
+      <c r="H13" t="n">
+        <v>240</v>
+      </c>
+      <c r="I13" t="n">
+        <v>200</v>
+      </c>
+      <c r="J13" t="n">
+        <v>1000</v>
+      </c>
+      <c r="K13" t="n">
+        <v>5</v>
+      </c>
+      <c r="L13" t="n">
+        <v>0</v>
+      </c>
+      <c r="M13" t="inlineStr"/>
+      <c r="N13" t="inlineStr">
+        <is>
+          <t>大师级锻造台，可锻造传说品质装备</t>
+        </is>
+      </c>
+      <c r="O13" t="inlineStr">
+        <is>
+          <t>tech_master_forge</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>wall_tier1</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>低矮土墙</t>
+        </is>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>wall</t>
+        </is>
+      </c>
+      <c r="D14" t="n">
+        <v>1</v>
+      </c>
+      <c r="E14" t="n">
+        <v>1</v>
+      </c>
+      <c r="F14" t="n">
+        <v>30</v>
+      </c>
+      <c r="G14" t="n">
+        <v>20</v>
+      </c>
+      <c r="H14" t="n">
+        <v>40</v>
+      </c>
+      <c r="I14" t="n">
+        <v>0</v>
+      </c>
+      <c r="J14" t="n">
+        <v>200</v>
+      </c>
+      <c r="K14" t="n">
+        <v>1</v>
+      </c>
+      <c r="L14" t="n">
+        <v>0</v>
+      </c>
+      <c r="M14" t="inlineStr"/>
+      <c r="N14" t="inlineStr">
+        <is>
+          <t>村子级别的低矮小墙，不能站人</t>
+        </is>
+      </c>
+      <c r="P14" t="n">
+        <v>1</v>
+      </c>
+      <c r="Q14" t="b">
+        <v>0</v>
+      </c>
+      <c r="R14" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>wall_tier2</t>
+        </is>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>标准城墙</t>
+        </is>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>wall</t>
+        </is>
+      </c>
+      <c r="D15" t="n">
+        <v>2</v>
+      </c>
+      <c r="E15" t="n">
+        <v>1</v>
+      </c>
+      <c r="F15" t="n">
+        <v>90</v>
+      </c>
+      <c r="G15" t="n">
+        <v>50</v>
+      </c>
+      <c r="H15" t="n">
+        <v>150</v>
+      </c>
+      <c r="I15" t="n">
+        <v>20</v>
+      </c>
+      <c r="J15" t="n">
+        <v>800</v>
+      </c>
+      <c r="K15" t="n">
+        <v>2</v>
+      </c>
+      <c r="L15" t="n">
+        <v>0</v>
+      </c>
+      <c r="M15" t="inlineStr"/>
+      <c r="N15" t="inlineStr">
+        <is>
+          <t>标准城墙，上面可以站人</t>
+        </is>
+      </c>
+      <c r="P15" t="n">
+        <v>2</v>
+      </c>
+      <c r="Q15" t="b">
+        <v>1</v>
+      </c>
+      <c r="R15" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>wall_tier3</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>大型城墙</t>
+        </is>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>wall</t>
+        </is>
+      </c>
+      <c r="D16" t="n">
+        <v>3</v>
+      </c>
+      <c r="E16" t="n">
+        <v>1</v>
+      </c>
+      <c r="F16" t="n">
+        <v>180</v>
+      </c>
+      <c r="G16" t="n">
+        <v>100</v>
+      </c>
+      <c r="H16" t="n">
+        <v>300</v>
+      </c>
+      <c r="I16" t="n">
+        <v>80</v>
+      </c>
+      <c r="J16" t="n">
+        <v>2000</v>
+      </c>
+      <c r="K16" t="n">
+        <v>3</v>
+      </c>
+      <c r="L16" t="n">
+        <v>0</v>
+      </c>
+      <c r="M16" t="inlineStr"/>
+      <c r="N16" t="inlineStr">
+        <is>
+          <t>上面能放一堆器械的大墙</t>
+        </is>
+      </c>
+      <c r="P16" t="n">
+        <v>3</v>
+      </c>
+      <c r="Q16" t="b">
+        <v>1</v>
+      </c>
+      <c r="R16" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>wall_gate</t>
+        </is>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>城门</t>
+        </is>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>wall_gate</t>
+        </is>
+      </c>
+      <c r="D17" t="n">
+        <v>2</v>
+      </c>
+      <c r="E17" t="n">
+        <v>1</v>
+      </c>
+      <c r="F17" t="n">
+        <v>120</v>
+      </c>
+      <c r="G17" t="n">
+        <v>80</v>
+      </c>
+      <c r="H17" t="n">
+        <v>100</v>
+      </c>
+      <c r="I17" t="n">
+        <v>30</v>
+      </c>
+      <c r="J17" t="n">
+        <v>500</v>
+      </c>
+      <c r="K17" t="n">
+        <v>2</v>
+      </c>
+      <c r="L17" t="n">
+        <v>0</v>
+      </c>
+      <c r="M17" t="inlineStr"/>
+      <c r="N17" t="inlineStr">
+        <is>
+          <t>城墙上的门，允许己方通行，可关闭拒敌</t>
+        </is>
+      </c>
+      <c r="P17" t="n">
+        <v>2</v>
+      </c>
+      <c r="Q17" t="b">
+        <v>0</v>
+      </c>
+      <c r="R17" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>moat</t>
+        </is>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>护城河</t>
+        </is>
+      </c>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>moat</t>
+        </is>
+      </c>
+      <c r="D18" t="n">
+        <v>1</v>
+      </c>
+      <c r="E18" t="n">
+        <v>1</v>
+      </c>
+      <c r="F18" t="n">
+        <v>20</v>
+      </c>
+      <c r="G18" t="n">
+        <v>0</v>
+      </c>
+      <c r="H18" t="n">
+        <v>0</v>
+      </c>
+      <c r="I18" t="n">
+        <v>0</v>
+      </c>
+      <c r="J18" t="n">
+        <v>9999</v>
+      </c>
+      <c r="K18" t="n">
+        <v>1</v>
+      </c>
+      <c r="L18" t="n">
+        <v>0</v>
+      </c>
+      <c r="M18" t="inlineStr"/>
+      <c r="N18" t="inlineStr">
+        <is>
+          <t>城墙外侧的沟渠，减缓/阻挡敌方移动</t>
+        </is>
+      </c>
+      <c r="P18" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q18" t="b">
+        <v>0</v>
+      </c>
+      <c r="R18" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>warehouse</t>
+        </is>
+      </c>
+      <c r="B19" t="inlineStr">
+        <is>
           <t>仓库</t>
+        </is>
+      </c>
+      <c r="C19" t="inlineStr">
+        <is>
+          <t>warehouse</t>
+        </is>
+      </c>
+      <c r="D19" t="n">
+        <v>1</v>
+      </c>
+      <c r="E19" t="n">
+        <v>16</v>
+      </c>
+      <c r="F19" t="n">
+        <v>60</v>
+      </c>
+      <c r="G19" t="n">
+        <v>120</v>
+      </c>
+      <c r="H19" t="n">
+        <v>40</v>
+      </c>
+      <c r="I19" t="n">
+        <v>0</v>
+      </c>
+      <c r="J19" t="n">
+        <v>300</v>
+      </c>
+      <c r="K19" t="n">
+        <v>0</v>
+      </c>
+      <c r="L19" t="n">
+        <v>0</v>
+      </c>
+      <c r="M19" t="inlineStr"/>
+      <c r="N19" t="inlineStr">
+        <is>
+          <t>储存建材，工人从此取货运往工地</t>
         </is>
       </c>
     </row>
